--- a/resources/app-mry/content/pricing/pricing_inr.xlsx
+++ b/resources/app-mry/content/pricing/pricing_inr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mehery Website\mehery.site\resources\app-mry\content\pricing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C955AAB-D2E4-4B07-96BC-3556F2CB6C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF17AD8A-6FB2-45F5-8C33-FF585B864B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="77">
   <si>
     <t>name</t>
   </si>
@@ -171,6 +171,84 @@
     <t>₹0.12</t>
   </si>
   <si>
+    <t>₹0.25</t>
+  </si>
+  <si>
+    <t>₹2.25</t>
+  </si>
+  <si>
+    <t>₹0.75</t>
+  </si>
+  <si>
+    <t>₹800</t>
+  </si>
+  <si>
+    <t>₹400</t>
+  </si>
+  <si>
+    <t>₹500</t>
+  </si>
+  <si>
+    <t>₹2,160</t>
+  </si>
+  <si>
+    <t>₹1,080</t>
+  </si>
+  <si>
+    <t>₹1,350</t>
+  </si>
+  <si>
+    <t>₹7,680</t>
+  </si>
+  <si>
+    <t>₹3,840</t>
+  </si>
+  <si>
+    <t>₹4,800</t>
+  </si>
+  <si>
+    <t>₹1,250</t>
+  </si>
+  <si>
+    <t>₹1,000</t>
+  </si>
+  <si>
+    <t>₹0</t>
+  </si>
+  <si>
+    <t>₹3,375</t>
+  </si>
+  <si>
+    <t>₹2,700</t>
+  </si>
+  <si>
+    <t>₹12,000</t>
+  </si>
+  <si>
+    <t>₹9,600</t>
+  </si>
+  <si>
+    <t>₹5,000</t>
+  </si>
+  <si>
+    <t>FREE</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>₹9,999</t>
+  </si>
+  <si>
+    <t>₹0.16</t>
+  </si>
+  <si>
+    <t>₹0.14</t>
+  </si>
+  <si>
     <t>₹0.08</t>
   </si>
   <si>
@@ -178,87 +256,6 @@
   </si>
   <si>
     <t>₹0.06</t>
-  </si>
-  <si>
-    <t>₹0.05</t>
-  </si>
-  <si>
-    <t>₹0.02</t>
-  </si>
-  <si>
-    <t>₹0.01</t>
-  </si>
-  <si>
-    <t>₹0.25</t>
-  </si>
-  <si>
-    <t>₹2.25</t>
-  </si>
-  <si>
-    <t>₹0.75</t>
-  </si>
-  <si>
-    <t>₹800</t>
-  </si>
-  <si>
-    <t>₹400</t>
-  </si>
-  <si>
-    <t>₹500</t>
-  </si>
-  <si>
-    <t>₹2,160</t>
-  </si>
-  <si>
-    <t>₹1,080</t>
-  </si>
-  <si>
-    <t>₹1,350</t>
-  </si>
-  <si>
-    <t>₹7,680</t>
-  </si>
-  <si>
-    <t>₹3,840</t>
-  </si>
-  <si>
-    <t>₹4,800</t>
-  </si>
-  <si>
-    <t>₹1,250</t>
-  </si>
-  <si>
-    <t>₹1,000</t>
-  </si>
-  <si>
-    <t>₹0</t>
-  </si>
-  <si>
-    <t>₹3,375</t>
-  </si>
-  <si>
-    <t>₹2,700</t>
-  </si>
-  <si>
-    <t>₹12,000</t>
-  </si>
-  <si>
-    <t>₹9,600</t>
-  </si>
-  <si>
-    <t>₹5,000</t>
-  </si>
-  <si>
-    <t>FREE</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Nil</t>
-  </si>
-  <si>
-    <t>₹9,999</t>
   </si>
 </sst>
 </file>
@@ -722,13 +719,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>35</v>
@@ -773,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>27</v>
@@ -796,13 +793,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>44</v>
@@ -814,43 +811,43 @@
         <v>47</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="U3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="W3" t="s">
         <v>30</v>
@@ -885,10 +882,10 @@
         <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>47</v>
@@ -900,31 +897,31 @@
         <v>5</v>
       </c>
       <c r="N4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="W4" t="s">
         <v>27</v>
@@ -959,10 +956,10 @@
         <v>47</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>47</v>
@@ -974,31 +971,31 @@
         <v>7</v>
       </c>
       <c r="N5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="Q5">
         <v>3</v>
       </c>
       <c r="R5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="W5" t="s">
         <v>27</v>
@@ -1018,7 +1015,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>39</v>
@@ -1033,46 +1030,46 @@
         <v>47</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <v>10</v>
       </c>
       <c r="N6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="Q6">
         <v>8</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="U6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="W6" t="s">
         <v>30</v>

--- a/resources/app-mry/content/pricing/pricing_inr.xlsx
+++ b/resources/app-mry/content/pricing/pricing_inr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mehery Website\mehery.site\resources\app-mry\content\pricing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF17AD8A-6FB2-45F5-8C33-FF585B864B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91EAED9-69E9-4AA9-889C-6C55BBABD28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
   <si>
     <t>name</t>
   </si>
@@ -45,9 +45,6 @@
     <t>fees.annualy</t>
   </si>
   <si>
-    <t>mfees.waba</t>
-  </si>
-  <si>
     <t>mfees.social</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>https://calendly.com/shekhars</t>
   </si>
   <si>
-    <t>Max 10/day</t>
-  </si>
-  <si>
     <t>₹2,499</t>
   </si>
   <si>
@@ -243,12 +237,6 @@
     <t>₹9,999</t>
   </si>
   <si>
-    <t>₹0.16</t>
-  </si>
-  <si>
-    <t>₹0.14</t>
-  </si>
-  <si>
     <t>₹0.08</t>
   </si>
   <si>
@@ -256,6 +244,24 @@
   </si>
   <si>
     <t>₹0.06</t>
+  </si>
+  <si>
+    <t>mfees.wabaMarketing</t>
+  </si>
+  <si>
+    <t>mfees.wabaUtil</t>
+  </si>
+  <si>
+    <t>₹0.10</t>
+  </si>
+  <si>
+    <t>₹0.05</t>
+  </si>
+  <si>
+    <t>₹0.02</t>
+  </si>
+  <si>
+    <t>10/day</t>
   </si>
 </sst>
 </file>
@@ -631,10 +637,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -654,431 +663,449 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2">
+        <v>78</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2">
         <v>1</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>27</v>
+      <c r="K4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>7</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R6">
+        <v>8</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X6" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s">
-        <v>30</v>
+      <c r="Y6" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>5</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="W4" t="s">
-        <v>27</v>
-      </c>
-      <c r="X4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5">
-        <v>3</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="W5" t="s">
-        <v>27</v>
-      </c>
-      <c r="X5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q6">
-        <v>8</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="W6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="E11" s="4"/>
     </row>
   </sheetData>

--- a/resources/app-mry/content/pricing/pricing_inr.xlsx
+++ b/resources/app-mry/content/pricing/pricing_inr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mehery Website\mehery.site\resources\app-mry\content\pricing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91EAED9-69E9-4AA9-889C-6C55BBABD28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB24268-0742-4F89-8880-F1CB200610A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,13 +255,13 @@
     <t>₹0.10</t>
   </si>
   <si>
-    <t>₹0.05</t>
-  </si>
-  <si>
-    <t>₹0.02</t>
-  </si>
-  <si>
     <t>10/day</t>
+  </si>
+  <si>
+    <t>₹0.14</t>
+  </si>
+  <si>
+    <t>₹0.18</t>
   </si>
 </sst>
 </file>
@@ -740,25 +740,25 @@
         <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>45</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>46</v>
@@ -906,7 +906,7 @@
         <v>70</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>45</v>

--- a/resources/app-mry/content/pricing/pricing_inr.xlsx
+++ b/resources/app-mry/content/pricing/pricing_inr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mehery Website\mehery.site\resources\app-mry\content\pricing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB24268-0742-4F89-8880-F1CB200610A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6E79B6-21D3-492E-AD8D-30964FD50998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>name</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>mfees.wabaUtil</t>
-  </si>
-  <si>
-    <t>₹0.10</t>
   </si>
   <si>
     <t>10/day</t>
@@ -740,25 +737,25 @@
         <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -829,7 +826,7 @@
         <v>45</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>46</v>
@@ -894,7 +891,7 @@
         <v>38</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>43</v>
@@ -906,7 +903,7 @@
         <v>70</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>45</v>
@@ -971,7 +968,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>43</v>
@@ -983,7 +980,7 @@
         <v>71</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>45</v>
@@ -1048,7 +1045,7 @@
         <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>44</v>
@@ -1060,7 +1057,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>45</v>
